--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488069_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488069_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1006</v>
+        <v>11.3678</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1829</v>
+        <v>9.309799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9176</v>
+        <v>2.058</v>
       </c>
       <c r="G2" t="n">
         <v>6.9445</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0105</v>
+        <v>2.2778</v>
       </c>
       <c r="T2" t="n">
-        <v>3.638</v>
+        <v>1.7649</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3725</v>
+        <v>0.5129</v>
       </c>
       <c r="V2" t="n">
         <v>2.3438</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7393</v>
+        <v>7.8474</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0455</v>
+        <v>6.2098</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6938</v>
+        <v>1.6376</v>
       </c>
       <c r="G3" t="n">
         <v>2.5876</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8493</v>
+        <v>1.9574</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9839</v>
+        <v>1.1481</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8093</v>
       </c>
       <c r="V3" t="n">
         <v>3.5006</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8268</v>
+        <v>4.8892</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6233</v>
+        <v>2.6857</v>
       </c>
       <c r="F4" t="n">
         <v>2.2035</v>
@@ -766,10 +766,10 @@
         <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7619</v>
+        <v>1.8243</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0573</v>
+        <v>1.1197</v>
       </c>
       <c r="U4" t="n">
         <v>0.7046</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6219</v>
+        <v>3.9245</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1708</v>
+        <v>2.9563</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4511</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2265</v>
+        <v>0.8907</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4095</v>
+        <v>2.1629</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8169999999999999</v>
+        <v>-1.2722</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0728</v>
+        <v>1.7335</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7353</v>
+        <v>1.0025</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3375</v>
+        <v>0.731</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.8428</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3258</v>
+        <v>1.1604</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5205</v>
+        <v>-2.0032</v>
       </c>
       <c r="P5" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.9733</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>1.7491</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5382</v>
+        <v>1.0068</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5817</v>
+        <v>0.7423</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>1.0864</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8953</v>
+        <v>3.5586</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4703</v>
+        <v>1.9671</v>
       </c>
       <c r="F6" t="n">
-        <v>0.425</v>
+        <v>1.5915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4745</v>
+        <v>2.2265</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9872</v>
+        <v>1.4095</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4617</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.385</v>
+        <v>3.0728</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2706</v>
+        <v>1.7353</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6556</v>
+        <v>1.3375</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9105</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2834</v>
+        <v>-0.3258</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1939</v>
+        <v>-0.5205</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2928</v>
+        <v>2.0566</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8187</v>
+        <v>1.3345</v>
       </c>
       <c r="U6" t="n">
-        <v>1.474</v>
+        <v>0.7221</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0612</v>
+        <v>0.2666</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3278</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8819</v>
+        <v>2.4004</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7733</v>
+        <v>2.3684</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1086</v>
+        <v>0.0319</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8907</v>
+        <v>0.4745</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1629</v>
+        <v>-0.9872</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2722</v>
+        <v>1.4617</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7335</v>
+        <v>1.385</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0025</v>
+        <v>-1.2706</v>
       </c>
       <c r="L7" t="n">
-        <v>0.731</v>
+        <v>2.6556</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8428</v>
+        <v>-0.9105</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1604</v>
+        <v>0.2834</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0032</v>
+        <v>-1.1939</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7065</v>
+        <v>1.7978</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1762</v>
+        <v>0.7169</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8827</v>
+        <v>1.0809</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0864</v>
+        <v>-1.0612</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1207</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6289</v>
+        <v>1.3576</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5431</v>
+        <v>-0.7863</v>
       </c>
       <c r="F8" t="n">
-        <v>2.172</v>
+        <v>2.1439</v>
       </c>
       <c r="G8" t="n">
         <v>0.2639</v>
@@ -1078,13 +1078,13 @@
         <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6405</v>
+        <v>1.3692</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7564</v>
+        <v>0.5131</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8841</v>
+        <v>0.8561</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8701</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7786</v>
+        <v>0.1104</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3677</v>
+        <v>1.9352</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1463</v>
+        <v>-1.8249</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8499</v>
+        <v>0.992</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9779</v>
+        <v>-1.2658</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8277</v>
+        <v>2.2577</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9607</v>
+        <v>1.7837</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2574</v>
+        <v>-0.5984</v>
       </c>
       <c r="L10" t="n">
-        <v>3.2181</v>
+        <v>2.3822</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1109</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2795</v>
+        <v>-0.6674</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3904</v>
+        <v>-0.1244</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>0.9911</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5606</v>
+        <v>0.5415</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3892</v>
+        <v>0.1515</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1714</v>
+        <v>0.39</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1979</v>
+        <v>-2.4142</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1979</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7993</v>
+        <v>-0.1746</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2222</v>
+        <v>0.7752</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0214</v>
+        <v>-0.9498</v>
       </c>
       <c r="G11" t="n">
-        <v>0.992</v>
+        <v>1.8499</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2658</v>
+        <v>-0.9779</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2577</v>
+        <v>2.8277</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7837</v>
+        <v>1.9607</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5984</v>
+        <v>-1.2574</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3822</v>
+        <v>3.2181</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.1109</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6674</v>
+        <v>0.2795</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1244</v>
+        <v>-0.3904</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9911</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3681</v>
+        <v>1.1646</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5616</v>
+        <v>0.7967</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1934</v>
+        <v>0.3679</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4142</v>
+        <v>-2.1979</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4142</v>
+        <v>-2.1979</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. MATEO HINOJO</t>
+          <t>A. GUZMAN SALINAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7986</v>
+        <v>-1.6858</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.795</v>
+        <v>-2.3435</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0036</v>
+        <v>0.6577</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.56</v>
+        <v>-1.0016</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.56</v>
+        <v>1.1354</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-2.1369</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3583</v>
+        <v>0.3802</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3583</v>
+        <v>2.1325</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.7523</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2018</v>
+        <v>-1.3818</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2018</v>
+        <v>-0.9971</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.3847</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7929</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5543</v>
+        <v>1.4959</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5543</v>
+        <v>0.5866</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.9093</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.9908</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GUZMAN SALINAS</t>
+          <t>P. MATEO HINOJO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2233</v>
+        <v>-2.2061</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8529</v>
+        <v>-2.2025</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6296</v>
+        <v>-0.0036</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0016</v>
+        <v>-1.56</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1354</v>
+        <v>-1.56</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1369</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3802</v>
+        <v>-1.3583</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1325</v>
+        <v>-1.3583</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7523</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3818</v>
+        <v>-0.2018</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9971</v>
+        <v>-0.2018</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3847</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1893</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9585</v>
+        <v>0.1469</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0772</v>
+        <v>0.1469</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8812</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9908</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9553</v>
+        <v>-3.9377</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9932</v>
+        <v>-0.8913</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9622</v>
+        <v>-3.0464</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3542</v>
@@ -1546,13 +1546,13 @@
         <v>0.1982</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1186</v>
+        <v>-0.1009</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3744</v>
+        <v>-0.2725</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2558</v>
+        <v>0.1716</v>
       </c>
       <c r="V14" t="n">
         <v>-2.6808</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>27.7423</v>
+        <v>28.0544</v>
       </c>
       <c r="E15" t="n">
-        <v>22.2745</v>
+        <v>22.5866</v>
       </c>
       <c r="F15" t="n">
-        <v>5.467700000000002</v>
+        <v>5.467599999999999</v>
       </c>
       <c r="G15" t="n">
         <v>17.0408</v>
@@ -1597,7 +1597,7 @@
         <v>9.279800000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>22.7874</v>
+        <v>22.78739999999999</v>
       </c>
       <c r="K15" t="n">
         <v>7.623600000000001</v>
@@ -1606,16 +1606,16 @@
         <v>15.1639</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.746799999999999</v>
+        <v>-5.7468</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1373</v>
+        <v>0.1373000000000004</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.884199999999999</v>
+        <v>-5.884199999999998</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.982200000000001</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q15" t="n">
         <v>-16.8487</v>
@@ -1624,13 +1624,13 @@
         <v>14.8665</v>
       </c>
       <c r="S15" t="n">
-        <v>15.9682</v>
+        <v>16.2802</v>
       </c>
       <c r="T15" t="n">
-        <v>8.700999999999999</v>
+        <v>9.013200000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>7.2668</v>
+        <v>7.266999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-3.2842</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7593</v>
+        <v>1.1533</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4733</v>
+        <v>2.4974</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7139</v>
+        <v>-1.3441</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7408</v>
+        <v>-1.1347</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1664</v>
+        <v>-1.8061</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5744</v>
+        <v>0.6713</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9262</v>
+        <v>1.637</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4351</v>
+        <v>-1.0147</v>
       </c>
       <c r="L16" t="n">
-        <v>2.491</v>
+        <v>2.6517</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1853</v>
+        <v>-2.7718</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2688</v>
+        <v>-0.7914</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9166</v>
+        <v>-1.9804</v>
       </c>
       <c r="P16" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6883</v>
+        <v>-1.6317</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5471</v>
+        <v>-0.8799</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2354</v>
+        <v>-0.7518</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.0772</v>
+        <v>1.5411</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.0772</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0769</v>
+        <v>1.0756</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1917</v>
+        <v>4.6583</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1149</v>
+        <v>-3.5827</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1347</v>
+        <v>2.7408</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8061</v>
+        <v>1.1664</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6713</v>
+        <v>1.5744</v>
       </c>
       <c r="J17" t="n">
-        <v>1.637</v>
+        <v>4.9262</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0147</v>
+        <v>2.4351</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6517</v>
+        <v>2.491</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7718</v>
+        <v>-2.1853</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7914</v>
+        <v>-1.2688</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9804</v>
+        <v>-0.9166</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3787</v>
+        <v>1.784</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3787</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7081</v>
+        <v>-1.372</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1855</v>
+        <v>-0.2679</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5226</v>
+        <v>-1.1041</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5411</v>
+        <v>-2.0772</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1992</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. ZARACHO PAEZ</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.884</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5926</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2913</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0198</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3361</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3559</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1007</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0605</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1205</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2756</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3961</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7055</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4919</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2136</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>O. ZARACHO PAEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5327</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.1852</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.3475</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.0198</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.3361</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.3559</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.1007</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.0605</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.1205</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.2756</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.3961</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3542</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.2698</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1651</v>
+        <v>-0.3584</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2565</v>
+        <v>0.9509</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4216</v>
+        <v>-1.3093</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8758</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9676</v>
+        <v>-1.1609</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5064</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4612</v>
+        <v>-0.3489</v>
       </c>
       <c r="V21" t="n">
         <v>0.0925</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2004</v>
+        <v>-0.5905</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4775</v>
+        <v>1.7831</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6778</v>
+        <v>-2.3735</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7332</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1747</v>
+        <v>-1.5648</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8736</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3011</v>
+        <v>-0.9968</v>
       </c>
       <c r="V22" t="n">
         <v>4.4914</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0787</v>
+        <v>-4.0944</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3005</v>
+        <v>-1.3359</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7782</v>
+        <v>-2.7585</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7941</v>
+        <v>-2.9444</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8622</v>
+        <v>-0.9508</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9319</v>
+        <v>-1.9936</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5517</v>
+        <v>-0.6949</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6722</v>
+        <v>-0.0196</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1205</v>
+        <v>-0.6752</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2424</v>
+        <v>-2.2495</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.19</v>
+        <v>-0.9312</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0524</v>
+        <v>-1.3184</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6201</v>
+        <v>-1.8987</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7488</v>
+        <v>-0.857</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1287</v>
+        <v>-1.0417</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6556</v>
+        <v>-0.4406</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6556</v>
+        <v>-1.6477</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5182</v>
+        <v>-4.2295</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5396</v>
+        <v>-1.1986</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9785</v>
+        <v>-3.0309</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9444</v>
+        <v>-1.7941</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9508</v>
+        <v>-0.8622</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9936</v>
+        <v>-0.9319</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6949</v>
+        <v>-0.5517</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0196</v>
+        <v>-0.6722</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6752</v>
+        <v>0.1205</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2495</v>
+        <v>-1.2424</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9312</v>
+        <v>-0.19</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3184</v>
+        <v>-1.0524</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.3225</v>
+        <v>-0.7709</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0608</v>
+        <v>-0.6469</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2618</v>
+        <v>-0.124</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4406</v>
+        <v>-2.6556</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6477</v>
+        <v>-2.6556</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.0902</v>
+        <v>-6.3439</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3985</v>
+        <v>-5.0021</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6917</v>
+        <v>-1.3419</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3895</v>
+        <v>-1.6535</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9173</v>
+        <v>-0.9282</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4721</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0761</v>
+        <v>0.9807</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0138</v>
+        <v>-0.2687</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.09</v>
+        <v>1.2494</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.3133</v>
+        <v>-2.6342</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9312</v>
+        <v>-0.6595</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.3822</v>
+        <v>-1.9747</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5858</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.9645</v>
+        <v>-4.9556</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3787</v>
+        <v>2.9733</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7516</v>
+        <v>-2.8008</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4351</v>
+        <v>-1.2938</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3165</v>
+        <v>-1.507</v>
       </c>
       <c r="V25" t="n">
-        <v>1.6366</v>
+        <v>0.0925</v>
       </c>
       <c r="W25" t="n">
-        <v>2.0772</v>
+        <v>0.2666</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4406</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.1001</v>
+        <v>-6.4006</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.2058</v>
+        <v>-4.0929</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8943</v>
+        <v>-2.3077</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.6535</v>
+        <v>-4.3895</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9282</v>
+        <v>-0.9173</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-3.4721</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9807</v>
+        <v>-1.0761</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2687</v>
+        <v>0.0138</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2494</v>
+        <v>-1.09</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.6342</v>
+        <v>-3.3133</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6595</v>
+        <v>-0.9312</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.9747</v>
+        <v>-2.3822</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.9822</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.9556</v>
+        <v>-3.9645</v>
       </c>
       <c r="R26" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.557</v>
+        <v>-2.062</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4975</v>
+        <v>-1.1295</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.0595</v>
+        <v>-0.9325</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0925</v>
+        <v>1.6366</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2666</v>
+        <v>2.0772</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.174</v>
+        <v>-0.4406</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.5205</v>
+        <v>-8.339</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.2256</v>
+        <v>-5.1237</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.2949</v>
+        <v>-3.2152</v>
       </c>
       <c r="G27" t="n">
         <v>-6.4473</v>
@@ -2560,13 +2560,13 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.8838</v>
+        <v>-1.7023</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9984</v>
+        <v>-0.8965</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8855</v>
+        <v>-0.8058</v>
       </c>
       <c r="V27" t="n">
         <v>0.6036</v>
@@ -2593,31 +2593,31 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-27.7424</v>
+        <v>-26.3841</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.4678</v>
+        <v>-5.467700000000003</v>
       </c>
       <c r="F28" t="n">
-        <v>-22.2745</v>
+        <v>-20.9163</v>
       </c>
       <c r="G28" t="n">
         <v>-17.0409</v>
       </c>
       <c r="H28" t="n">
-        <v>-7.7611</v>
+        <v>-7.761100000000001</v>
       </c>
       <c r="I28" t="n">
         <v>-9.279999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>5.746599999999999</v>
+        <v>5.746600000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1376000000000008</v>
+        <v>-0.1376000000000004</v>
       </c>
       <c r="L28" t="n">
-        <v>5.883999999999999</v>
+        <v>5.884</v>
       </c>
       <c r="M28" t="n">
         <v>-22.7874</v>
@@ -2638,13 +2638,13 @@
         <v>16.8489</v>
       </c>
       <c r="S28" t="n">
-        <v>-15.9682</v>
+        <v>-14.6099</v>
       </c>
       <c r="T28" t="n">
-        <v>-7.267100000000001</v>
+        <v>-7.266999999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>-8.7013</v>
+        <v>-7.3428</v>
       </c>
       <c r="V28" t="n">
         <v>3.2843</v>
